--- a/Assets/Notes/大盘构型_面板元素表.xlsx
+++ b/Assets/Notes/大盘构型_面板元素表.xlsx
@@ -620,7 +620,11 @@
           <t>Notice Text（限 62 ）；3-ArmorText</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>show</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Card Info Text（限60字）</t>
@@ -676,12 +680,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>血量图标</t>
+          <t>血量图标；5-HpText</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>血量图标</t>
+          <t>血量图标；5-HpText</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -691,7 +695,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>血量图标</t>
+          <t>血量图标；5-HpText</t>
         </is>
       </c>
       <c r="H6" s="3" t="n"/>
@@ -710,12 +714,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>攻击图标；6-HpText</t>
+          <t>攻击图标；6-AttackText</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>攻击图标；6-HpText；6-AttackText</t>
+          <t>攻击图标；6-AttackText</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -725,7 +729,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>攻击图标；6-HpText；6-AttackText</t>
+          <t>攻击图标；6-AttackText</t>
         </is>
       </c>
       <c r="H7" s="3" t="n"/>
@@ -744,7 +748,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>防御图标；7-AttackText</t>
+          <t>防御图标；7-ArmorText</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -754,12 +758,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>防御图标</t>
+          <t>防御图标；7-ArmorText</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>防御图标</t>
+          <t>防御图标；7-ArmorText</t>
         </is>
       </c>
       <c r="H8" s="3" t="n"/>
@@ -810,7 +814,7 @@
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>RelicPanelAnchors</t>
+          <t>DeckRelicPanelAnchors</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -878,7 +882,7 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CardDeckAnchors；12-ArmorText</t>
+          <t>CardDeckAnchors</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -888,12 +892,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>CardDeckAnchors；12-HpText；12-AttackText；12-ArmorText</t>
+          <t>DeckCardDeckAnchors；12-HpText；12-AttackText</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>CardDeckAnchors；12-ArmorText</t>
+          <t>CardDeckAnchors</t>
         </is>
       </c>
       <c r="H13" s="3" t="n"/>
